--- a/0_Документы/квитанции_кредит/кредит_оплата.xlsx
+++ b/0_Документы/квитанции_кредит/кредит_оплата.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS\apartment\0_Документы\квитанции_кредит\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3296110-CA6B-43A2-9B8C-7B3DF2A073D4}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4794140E-3124-4ABE-B7CA-BE76A69FA372}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -145,7 +145,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -153,6 +153,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="2" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="3" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Нейтральный" xfId="3" builtinId="28"/>
@@ -227,18 +228,10 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:strRef>
-              <c:f>Лист1!$E$6</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>проценты</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>сумма внесенная</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -263,10 +256,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Лист1!$A$7:$A$16</c:f>
+              <c:f>Лист1!$A$7:$A$18</c:f>
               <c:numCache>
                 <c:formatCode>dd\.mm\.yyyy</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>45810</c:v>
                 </c:pt>
@@ -296,45 +289,57 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="m/d/yyyy">
+                  <c:v>46082</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="m/d/yyyy">
+                  <c:v>46113</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Лист1!$E$7:$E$16</c:f>
+              <c:f>Лист1!$B$7:$B$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>302.88</c:v>
+                  <c:v>2000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>921.6</c:v>
+                  <c:v>2000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>923.24</c:v>
+                  <c:v>2000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>848.4</c:v>
+                  <c:v>2000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>920.67</c:v>
+                  <c:v>2000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>875.33</c:v>
+                  <c:v>2000</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>9000</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>756.04</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>739.77</c:v>
+                  <c:v>6000</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>561.03</c:v>
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -342,7 +347,134 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C2EC-4279-A7AB-3A113FF9DFF0}"/>
+              <c16:uniqueId val="{00000000-67CD-45ED-B5AF-F0DC6836795B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>погашение долга</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Лист1!$A$7:$A$18</c:f>
+              <c:numCache>
+                <c:formatCode>dd\.mm\.yyyy</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>45810</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45842</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45871</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45903</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45933</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45965</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45983</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45992</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46025</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="m/d/yyyy">
+                  <c:v>46082</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="m/d/yyyy">
+                  <c:v>46113</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Лист1!$F$7:$F$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1697.12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1078.4000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1076.76</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1151.5999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1079.33</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1124.67</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4243.96</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5260.23</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5438.97</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7525.73</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4570.41</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-67CD-45ED-B5AF-F0DC6836795B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -354,16 +486,157 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="855593759"/>
-        <c:axId val="911949967"/>
+        <c:axId val="1298436447"/>
+        <c:axId val="1298428543"/>
+      </c:scatterChart>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>проценты</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Лист1!$A$7:$A$18</c:f>
+              <c:numCache>
+                <c:formatCode>dd\.mm\.yyyy</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>45810</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45842</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45871</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45903</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45933</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45965</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45983</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45992</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46025</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="m/d/yyyy">
+                  <c:v>46082</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="m/d/yyyy">
+                  <c:v>46113</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Лист1!$E$7:$E$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>302.88</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>921.6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>923.24</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>848.4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>920.67</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>875.33</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>756.04</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>739.77</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>561.03</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>474.27</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>429.59</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-67CD-45ED-B5AF-F0DC6836795B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1239555487"/>
+        <c:axId val="1239544671"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="855593759"/>
+        <c:axId val="1298428543"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="b"/>
+        <c:axPos val="r"/>
         <c:majorGridlines>
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -378,20 +651,14 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="dd\.mm\.yyyy" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -415,45 +682,39 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="911949967"/>
-        <c:crosses val="autoZero"/>
+        <c:crossAx val="1298436447"/>
+        <c:crosses val="max"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="911949967"/>
+        <c:axId val="1298436447"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="dd\.mm\.yyyy" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1298428543"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1239544671"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -477,8 +738,21 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="855593759"/>
-        <c:crosses val="autoZero"/>
+        <c:crossAx val="1239555487"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1239555487"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="dd\.mm\.yyyy" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1239544671"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
@@ -489,6 +763,37 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:extLst>
@@ -574,7 +879,7 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -601,8 +906,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -703,7 +1008,7 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+      <a:ln w="28575" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -735,10 +1040,10 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -778,23 +1083,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -899,8 +1203,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -1032,20 +1336,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -1059,17 +1362,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -1094,22 +1386,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>4762</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>80962</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Диаграмма 1">
+        <xdr:cNvPr id="3" name="Диаграмма 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BE81D92-FD66-40ED-9811-48B42E3F490D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B36E8552-FC4F-4472-860D-D064C5ECC157}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1348,8 +1640,8 @@
         <v>9</v>
       </c>
       <c r="J1">
-        <f>SUM(F7:F16)</f>
-        <v>31151.040000000001</v>
+        <f>SUM(F7:F18)</f>
+        <v>43247.180000000008</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1358,14 +1650,14 @@
       </c>
       <c r="F2" s="4">
         <f>F1-J1</f>
-        <v>35848.959999999999</v>
+        <v>23752.819999999992</v>
       </c>
       <c r="I2" t="s">
         <v>7</v>
       </c>
       <c r="J2" s="5">
-        <f>SUM(E7:E16)</f>
-        <v>6848.96</v>
+        <f>SUM(E7:E18)</f>
+        <v>7752.82</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1374,7 +1666,7 @@
       </c>
       <c r="J3" s="6">
         <f>J1+J2</f>
-        <v>38000</v>
+        <v>51000.000000000007</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1393,6 +1685,10 @@
       <c r="H6" t="s">
         <v>4</v>
       </c>
+      <c r="I6">
+        <f>SUM(H7:H18)</f>
+        <v>51000</v>
+      </c>
     </row>
     <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
@@ -1574,18 +1870,54 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="7">
+        <v>46082</v>
+      </c>
+      <c r="B17">
+        <v>8000</v>
+      </c>
+      <c r="E17">
+        <v>474.27</v>
+      </c>
+      <c r="F17">
+        <v>7525.73</v>
+      </c>
+      <c r="H17">
+        <f>E17+F17</f>
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7">
+        <v>46113</v>
+      </c>
+      <c r="B18">
+        <v>5000</v>
+      </c>
+      <c r="E18">
+        <v>429.59</v>
+      </c>
+      <c r="F18">
+        <v>4570.41</v>
+      </c>
+      <c r="H18">
+        <f>E18+F18</f>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
